--- a/stories/arbres/ATOM-VIV.PLA.001-12.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-12.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Émeline est dans le jardin. Le pied de tomate a des feuilles. Papa, l'adulte, prend l'arrosoir. Papa dit : la plante a besoin d'eau. Elle a besoin de lumière. Émeline tient l'arrosoir avec papa. Ils arrosent. L'eau tombe sur la terre. La terre devient foncée. Parce qu'il y a de l'eau et de la lumière, la plante grandit. Plus tard, maman montre le thym à la fenêtre. Même leçon, autre lieu. Maman, l'adulte, ouvre le store. La lumière arrive. Émeline arrose avec maman. L'eau sent le thym. Émeline pose l'arrosoir. L'adulte est là.</t>
+          <t>Émeline est dans le jardin. Le pied de tomate a des feuilles. Papa, l'adulte, prend l'arrosoir. La plante a besoin d'eau. Elle a besoin de lumière. Émeline tient l'arrosoir avec papa. Ils arrosent. L'eau tombe sur la terre. La terre devient foncée. Parce qu'il y a de l'eau et de la lumière, la plante grandit. Plus tard, maman montre le thym à la fenêtre. Même leçon, autre lieu. Maman, l'adulte, ouvre le store. La lumière arrive. Émeline arrose avec maman. L'eau sent le thym. Émeline pose l'arrosoir. L'adulte est là.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Émeline est dans le jardin. Le pied de tomate a des feuilles. Papa, l'adulte, prend l'arrosoir.
+papa|La plante a besoin d'eau. Elle a besoin de lumière.
+narrateur|Émeline tient l'arrosoir avec papa. Ils arrosent. L'eau tombe sur la terre. La terre devient foncée. Parce qu'il y a de l'eau et de la lumière, la plante grandit. Plus tard, maman montre le thym à la fenêtre. Même leçon, autre lieu. Maman, l'adulte, ouvre le store. La lumière arrive. Émeline arrose avec maman. L'eau sent le thym. Émeline pose l'arrosoir. L'adulte est là.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Émeline s'occupe des plantes. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Émeline a arrosé. Il y a de l'eau et de la lumière. Papa et maman, les adultes, étaient là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Émeline essuie ses mains. Le thym brille.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.PLA.001-12.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-12.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,11 @@
 narrateur|Émeline tient l'arrosoir avec papa. Ils arrosent. L'eau tombe sur la terre. La terre devient foncée. Parce qu'il y a de l'eau et de la lumière, la plante grandit. Plus tard, maman montre le thym à la fenêtre. Même leçon, autre lieu. Maman, l'adulte, ouvre le store. La lumière arrive. Émeline arrose avec maman. L'eau sent le thym. Émeline pose l'arrosoir. L'adulte est là.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1505,7 @@
           <t>narrateur|Émeline s'occupe des plantes. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1677,7 @@
           <t>narrateur|Émeline a arrosé. Il y a de l'eau et de la lumière. Papa et maman, les adultes, étaient là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1845,7 @@
           <t>narrateur|Émeline essuie ses mains. Le thym brille.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.PLA.001-12.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-12.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Émeline arrose la tomate et le thym</t>
+          <t>La sauce du jardin de Raphaël</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Raphaël veut une sauce qui sent le jardin. L'arrosoir est vide. Il arrose la tomate avec papa, le thym avec maman. La casserole sent le thym.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Émeline est dans le jardin. Le pied de tomate a des feuilles. Papa, l'adulte, prend l'arrosoir. La plante a besoin d'eau. Elle a besoin de lumière. Émeline tient l'arrosoir avec papa. Ils arrosent. L'eau tombe sur la terre. La terre devient foncée. Parce qu'il y a de l'eau et de la lumière, la plante grandit. Plus tard, maman montre le thym à la fenêtre. Même leçon, autre lieu. Maman, l'adulte, ouvre le store. La lumière arrive. Émeline arrose avec maman. L'eau sent le thym. Émeline pose l'arrosoir. L'adulte est là.</t>
+          <t>Le gravier du jardin craque sous les pas. Une casserole attend déjà dans la cuisine. Dehors, le pied de tomate a des feuilles tièdes. Deux tomates pendent, encore un peu vertes. Tu sens la terre, Raphaël ? Oui, papa. Je veux une sauce du jardin. Avec du thym, alors. D'abord la tomate. En ce moment, Raphaël soulève l'arrosoir. L'arrosoir est trop léger. Il n'y a plus d'eau. On le remplit au robinet ? Oui. L'eau tape le métal, tout fort, puis tout doux. La plante a besoin d'eau. Elle a besoin de lumière. Ils versent au pied de la tomate. La terre devient foncée. Elle boit. Le thym, lui, est à la fenêtre. On y va après ? Après, pour la sauce. Raphaël pose l'arrosoir un moment. Une coccinelle traverse une feuille, puis s'en va. On va au thym, maman ? Oui, à la fenêtre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Émeline est dans le jardin. Le pied de tomate a des feuilles. Papa, l'adulte, prend l'arrosoir. Papa dit : la plante a besoin d'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. Elle a besoin de lumière. Émeline tient l'arrosoir avec papa. Ils arrosent. L'eau tombe sur la terre. La terre devient foncée. Parce qu'il y a de l'eau et de la lumière, la plante grandit. Plus tard, maman montre le thym à la fenêtre. Même leçon, autre lieu. Maman, l'adulte, ouvre le store. La lumière arrive. Émeline arrose avec maman. L'eau sent le thym. Émeline pose l'arrosoir. L'adulte est là.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le gravier du jardin craque sous les pas. Une casserole attend déjà dans la cuisine. Dehors, le pied de tomate a des feuilles tièdes. Deux tomates pendent, encore un peu vertes. Tu sens la terre, Raphaël ? Oui, papa. Je veux une sauce du jardin. Avec du thym, alors. D'abord la tomate. En ce moment, Raphaël soulève l'arrosoir. L'arrosoir est trop léger. Il n'y a plus d'eau. On le remplit au robinet ? Oui. L'eau tape le métal, tout fort, puis tout doux. La plante a besoin d'eau. Elle a besoin de lumière. Ils versent au pied de la tomate. La terre devient foncée. Elle boit. Le thym, lui, est à la fenêtre. On y va après ? Après, pour la sauce. Raphaël pose l'arrosoir un moment. Une coccinelle traverse une feuille, puis s'en va. On va au thym, maman ? Oui, à la fenêtre.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,9 +1324,33 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Émeline est dans le jardin. Le pied de tomate a des feuilles. Papa, l'adulte, prend l'arrosoir.
-papa|La plante a besoin d'eau. Elle a besoin de lumière.
-narrateur|Émeline tient l'arrosoir avec papa. Ils arrosent. L'eau tombe sur la terre. La terre devient foncée. Parce qu'il y a de l'eau et de la lumière, la plante grandit. Plus tard, maman montre le thym à la fenêtre. Même leçon, autre lieu. Maman, l'adulte, ouvre le store. La lumière arrive. Émeline arrose avec maman. L'eau sent le thym. Émeline pose l'arrosoir. L'adulte est là.</t>
+          <t>narrateur|Le gravier du jardin craque sous les pas.
+narrateur|Une casserole attend déjà dans la cuisine.
+narrateur|Dehors, le pied de tomate a des feuilles tièdes.
+narrateur|Deux tomates pendent, encore un peu vertes.
+papa|Tu sens la terre, Raphaël ?
+enfant-m|Oui, papa.
+enfant-m|Je veux une sauce du jardin.
+maman|Avec du thym, alors.
+papa|D'abord la tomate.
+narrateur|En ce moment, Raphaël soulève l'arrosoir.
+narrateur|L'arrosoir est trop léger.
+enfant-m|Il n'y a plus d'eau.
+papa|On le remplit au robinet ?
+enfant-m|Oui.
+narrateur|L'eau tape le métal, tout fort, puis tout doux.
+papa|La plante a besoin d'eau.
+papa|Elle a besoin de lumière.
+narrateur|Ils versent au pied de la tomate.
+narrateur|La terre devient foncée.
+enfant-m|Elle boit.
+maman|Le thym, lui, est à la fenêtre.
+papa|On y va après ?
+enfant-m|Après, pour la sauce.
+narrateur|Raphaël pose l'arrosoir un moment.
+narrateur|Une coccinelle traverse une feuille, puis s'en va.
+enfant-m|On va au thym, maman ?
+maman|Oui, à la fenêtre.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1346,19 +1382,19 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Raphaël s'occupe des plantes. Que fait-il ?</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Raphaël s'occupe des plantes. Que fait-il ?</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>Émeline s'occupe des plantes. Que fait-elle ?</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Émeline s'occupe des plantes. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Émeline s'occupe des plantes. Que fait-elle ?</t>
-        </is>
-      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>arroser</t>
@@ -1366,7 +1402,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>arroser | elle arrose | de l'eau | avec papa | avec l'adulte</t>
+          <t>arroser | de l'eau | eau | lumière | tomate | thym</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1381,7 +1417,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle arrose avec l'adulte. Que fait Émeline ?</t>
+          <t>Il arrose. Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1423,14 +1459,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1502,10 +1538,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Émeline s'occupe des plantes. Que fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Raphaël s'occupe des plantes.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1530,12 +1566,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Émeline a arrosé. Il y a de l'eau et de la lumière. Papa et maman, les adultes, étaient là.</t>
+          <t>Dans la cuisine, le store de la fenêtre est fermé. Le thym est dans l'ombre, un peu terne. Il n'a pas de lumière, tu vois ? On ouvre le store ? Oui, doucement. Raphaël tire le store avec maman. Le jour arrive sur les tiges. Maintenant, un peu d'eau. Papa tend l'arrosoir. Il est encore un peu lourd. Avec toi, maman. Oui, avec un adulte. Ils versent un filet au pied du thym. L'eau sent déjà l'herbe. Deux arrosages, alors. La tomate, et le thym. Merci, Raphaël. Pour la sauce. On coupe une branche, tout petit ? Une seule, le pied reste. Raphaël tient la petite branche. Ses doigts sentent le jardin.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Émeline a arrosé. Il y a de l'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt; et de la lumière. Papa et maman, les adultes, étaient là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Dans la cuisine, le store de la fenêtre est fermé. Le thym est dans l'ombre, un peu terne. Il n'a pas de lumière, tu vois ? On ouvre le store ? Oui, doucement. Raphaël tire le store avec maman. Le jour arrive sur les tiges. Maintenant, un peu d'eau. Papa tend l'arrosoir. Il est encore un peu lourd. Avec toi, maman. Oui, avec un adulte. Ils versent un filet au pied du thym. L'eau sent déjà l'herbe. Deux arrosages, alors. La tomate, et le thym. Merci, Raphaël. Pour la sauce. On coupe une branche, tout petit ? Une seule, le pied reste. Raphaël tient la petite branche. Ses doigts sentent le jardin.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1598,7 +1634,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1674,10 +1710,30 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Émeline a arrosé. Il y a de l'eau et de la lumière. Papa et maman, les adultes, étaient là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Dans la cuisine, le store de la fenêtre est fermé.
+narrateur|Le thym est dans l'ombre, un peu terne.
+maman|Il n'a pas de lumière, tu vois ?
+enfant-m|On ouvre le store ?
+maman|Oui, doucement.
+narrateur|Raphaël tire le store avec maman.
+narrateur|Le jour arrive sur les tiges.
+maman|Maintenant, un peu d'eau.
+narrateur|Papa tend l'arrosoir.
+narrateur|Il est encore un peu lourd.
+enfant-m|Avec toi, maman.
+maman|Oui, avec un adulte.
+narrateur|Ils versent un filet au pied du thym.
+narrateur|L'eau sent déjà l'herbe.
+papa|Deux arrosages, alors.
+papa|La tomate, et le thym.
+maman|Merci, Raphaël.
+enfant-m|Pour la sauce.
+papa|On coupe une branche, tout petit ?
+maman|Une seule, le pied reste.
+narrateur|Raphaël tient la petite branche.
+narrateur|Ses doigts sentent le jardin.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1702,12 +1758,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Émeline essuie ses mains. Le thym brille.</t>
+          <t>Maman fait chauffer la casserole. Papa coupe deux tomates du jardin. Le jus tombe dans la sauce, tout rouge. Le thym, maintenant ? Oui, tes doigts tout doux. Raphaël effeuille la petite branche. Les feuilles tombent dans le rouge. Tu sens ? Ça sent le jardin. La tomate et le thym, ensemble. La vapeur monte, un peu verte, un peu sucrée. On a arrosé, avant. Deux fois. Oui, l'eau et la lumière.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Émeline essuie ses &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s. Le thym brille.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman fait chauffer la casserole. Papa coupe deux tomates du jardin. Le jus tombe dans la sauce, tout rouge. Le thym, maintenant ? Oui, tes doigts tout doux. Raphaël effeuille la petite branche. Les feuilles tombent dans le rouge. Tu sens ? Ça sent le jardin. La tomate et le thym, ensemble. La vapeur monte, un peu verte, un peu sucrée. On a arrosé, avant. Deux fois. Oui, l'eau et la lumière.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1770,7 +1826,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1842,10 +1898,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Émeline essuie ses mains. Le thym brille.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Maman fait chauffer la casserole.
+narrateur|Papa coupe deux tomates du jardin.
+narrateur|Le jus tombe dans la sauce, tout rouge.
+enfant-m|Le thym, maintenant ?
+maman|Oui, tes doigts tout doux.
+narrateur|Raphaël effeuille la petite branche.
+narrateur|Les feuilles tombent dans le rouge.
+papa|Tu sens ?
+enfant-m|Ça sent le jardin.
+maman|La tomate et le thym, ensemble.
+narrateur|La vapeur monte, un peu verte, un peu sucrée.
+papa|On a arrosé, avant.
+enfant-m|Deux fois.
+maman|Oui, l'eau et la lumière.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1870,12 +1938,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La casserole chuchote tout bas. La sauce est prête ? Bientôt. Elle sent déjà le jardin. Le thym brille encore au rebord. La vapeur sent le jardin, tout entier.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La casserole chuchote tout bas. La sauce est prête ? Bientôt. Elle sent déjà le jardin. Le thym brille encore au rebord. La vapeur sent le jardin, tout entier.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1938,7 +2006,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2010,10 +2078,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|La casserole chuchote tout bas.
+enfant-m|La sauce est prête ?
+papa|Bientôt.
+maman|Elle sent déjà le jardin.
+narrateur|Le thym brille encore au rebord.
+narrateur|La vapeur sent le jardin, tout entier.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2032,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2142,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.PLA.001-12.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-12.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin puis rebord de fenêtre</t>
+          <t>jardin puis cuisine, rebord de fenêtre</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Émeline, papa, maman</t>
+          <t>Raphaël, papa, maman</t>
         </is>
       </c>
     </row>
